--- a/data/trans_orig/Q5409-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5409-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la orina (incontinencia) en 2007</t>
+          <t>Población según si se le escapa la orina (incontinencia) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,97 +733,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2080</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,62 +881,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1769</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>6327</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1769</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>6153</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>54205</t>
+          <t>53544</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29709</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83340</t>
+          <t>83166</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1189,97 +1189,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1302,97 +1302,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50830</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66616</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>942</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>2103</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11446</t>
+          <t>11165</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61526</t>
+          <t>60648</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69948</t>
+          <t>69884</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16107</t>
+          <t>15754</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23205</t>
+          <t>23238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80259</t>
+          <t>80357</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91426</t>
+          <t>91482</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10841</t>
+          <t>11412</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25277</t>
+          <t>25231</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30480</t>
+          <t>32093</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>231443</t>
+          <t>231508</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>247478</t>
+          <t>247575</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72810</t>
+          <t>72734</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>82790</t>
+          <t>83434</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>309869</t>
+          <t>307217</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>328155</t>
+          <t>327389</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9646</t>
+          <t>9822</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11672</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>9864</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>4446</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16753</t>
+          <t>17265</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7725</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22029</t>
+          <t>22109</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43314</t>
+          <t>42513</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52592</t>
+          <t>52683</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>75151</t>
+          <t>74444</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89565</t>
+          <t>89181</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>123064</t>
+          <t>122758</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>140525</t>
+          <t>140201</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,41%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7786</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23138</t>
+          <t>22244</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22887</t>
+          <t>23024</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16002</t>
+          <t>17033</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37173</t>
+          <t>37810</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17507</t>
+          <t>17252</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>37530</t>
+          <t>37473</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>371035</t>
+          <t>372180</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>396673</t>
+          <t>397788</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>375887</t>
+          <t>376382</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>401465</t>
+          <t>401565</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>2557</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12077</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13325</t>
+          <t>13187</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31831</t>
+          <t>31630</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18169</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39406</t>
+          <t>40066</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>18510</t>
+          <t>19899</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>37941</t>
+          <t>40277</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29399</t>
+          <t>29389</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55089</t>
+          <t>54812</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>53338</t>
+          <t>53425</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>85358</t>
+          <t>84061</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>456645</t>
+          <t>455979</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>478138</t>
+          <t>477175</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>598254</t>
+          <t>599640</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>628518</t>
+          <t>629432</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1062185</t>
+          <t>1063805</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1101828</t>
+          <t>1100381</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,38%</t>
         </is>
       </c>
     </row>
@@ -3964,7 +3964,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la orina (incontinencia) en 2012</t>
+          <t>Población según si se le escapa la orina (incontinencia) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4159,97 +4159,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2151</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2091</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2171</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12233</t>
+          <t>11907</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,21%</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33323</t>
+          <t>34724</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18765</t>
+          <t>18364</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56974</t>
+          <t>57300</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68142</t>
+          <t>68152</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -4615,97 +4615,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1113</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2230</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4796</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5,89%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>25,37%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1113</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>4620</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>5257</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>24,44%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1113</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4680</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9310</t>
+          <t>10049</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>4680</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11546</t>
+          <t>11732</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>51320</t>
+          <t>50581</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59621</t>
+          <t>59554</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12929</t>
+          <t>12289</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66808</t>
+          <t>66229</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77293</t>
+          <t>77333</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6176</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>5806</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6902</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15446</t>
+          <t>14681</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19762</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102174</t>
+          <t>102635</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115570</t>
+          <t>115667</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44135</t>
+          <t>43436</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52687</t>
+          <t>52645</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152173</t>
+          <t>152076</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>167119</t>
+          <t>167114</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2108</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12655</t>
+          <t>13647</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>15253</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13118</t>
+          <t>15120</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35956</t>
+          <t>37386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15322</t>
+          <t>15515</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22488</t>
+          <t>21890</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45417</t>
+          <t>45882</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>188889</t>
+          <t>187949</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>213402</t>
+          <t>212238</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42474</t>
+          <t>41857</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54785</t>
+          <t>54570</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>236048</t>
+          <t>238045</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>262036</t>
+          <t>262803</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>90,05%</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>12046</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29947</t>
+          <t>29505</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14008</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32419</t>
+          <t>32401</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4299</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>15827</t>
+          <t>16634</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12485</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>30327</t>
+          <t>29070</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19678</t>
+          <t>20152</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>40991</t>
+          <t>38967</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84120</t>
+          <t>84351</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97176</t>
+          <t>97346</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>136244</t>
+          <t>136227</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>159723</t>
+          <t>159354</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>225429</t>
+          <t>226427</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>251034</t>
+          <t>252660</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,8%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14400</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34040</t>
+          <t>33211</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>13904</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33808</t>
+          <t>33125</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27147</t>
+          <t>26771</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50545</t>
+          <t>51826</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27202</t>
+          <t>27122</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50273</t>
+          <t>50431</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -6665,12 +6665,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6680,12 +6680,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>318348</t>
+          <t>318526</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>348556</t>
+          <t>348160</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,12 +6715,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>318751</t>
+          <t>321152</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>350367</t>
+          <t>350663</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,4%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33919</t>
+          <t>34843</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62785</t>
+          <t>62451</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>43303</t>
+          <t>42560</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>73518</t>
+          <t>73279</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>31083</t>
+          <t>29896</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>61605</t>
+          <t>59091</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>57599</t>
+          <t>57175</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>90823</t>
+          <t>90047</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>98957</t>
+          <t>98558</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>141791</t>
+          <t>142096</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>486674</t>
+          <t>490906</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>519142</t>
+          <t>521194</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>597352</t>
+          <t>602435</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>639744</t>
+          <t>641473</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1099465</t>
+          <t>1097573</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1150224</t>
+          <t>1149817</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,34%</t>
         </is>
       </c>
     </row>
@@ -7390,7 +7390,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la orina (incontinencia) en 2016</t>
+          <t>Población según si se le escapa la orina (incontinencia) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7585,97 +7585,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2085</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1536</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12579</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10887</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4752</t>
+          <t>4546</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18850</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>16,88%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>56068</t>
+          <t>55876</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67111</t>
+          <t>67155</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26001</t>
+          <t>26251</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35679</t>
+          <t>35611</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>86685</t>
+          <t>87724</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100783</t>
+          <t>100989</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -8041,97 +8041,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2137</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>12,15%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>51,85%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>2137</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>8621</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>12,15%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>10965</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>49,02%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2137</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>9924</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7734</t>
+          <t>7422</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>994</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8717</t>
+          <t>9107</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45610</t>
+          <t>45922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52477</t>
+          <t>52483</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56929</t>
+          <t>57473</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68863</t>
+          <t>68922</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8532,62 +8532,62 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>2322</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>6163</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>1705</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>5890</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>2546</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>11672</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10570</t>
+          <t>10685</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18092</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106421</t>
+          <t>106286</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116684</t>
+          <t>116797</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35639</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44988</t>
+          <t>45109</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146616</t>
+          <t>146259</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159637</t>
+          <t>159439</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2318</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13552</t>
+          <t>13133</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17834</t>
+          <t>17621</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21489</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>18426</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14426</t>
+          <t>13802</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34722</t>
+          <t>32229</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>177800</t>
+          <t>178562</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>192168</t>
+          <t>193255</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>74538</t>
+          <t>74143</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>91542</t>
+          <t>90905</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>257748</t>
+          <t>258689</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>280185</t>
+          <t>281069</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12856</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>19544</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7520</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20300</t>
+          <t>21013</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9327</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25884</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19680</t>
+          <t>20088</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>39671</t>
+          <t>41382</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,58%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>120368</t>
+          <t>120583</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134617</t>
+          <t>134663</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>127303</t>
+          <t>126724</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>145702</t>
+          <t>146429</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>252969</t>
+          <t>250646</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>276888</t>
+          <t>276186</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,62%</t>
         </is>
       </c>
     </row>
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31495</t>
+          <t>31497</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12374</t>
+          <t>11782</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31495</t>
+          <t>31497</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30161</t>
+          <t>29558</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55481</t>
+          <t>57023</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30161</t>
+          <t>29558</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55481</t>
+          <t>57023</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>335098</t>
+          <t>333382</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>366248</t>
+          <t>365662</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>335098</t>
+          <t>333382</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>366248</t>
+          <t>365662</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,52%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>15601</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23295</t>
+          <t>23755</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>48616</t>
+          <t>49539</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31196</t>
+          <t>30484</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>60950</t>
+          <t>58560</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>30132</t>
+          <t>30442</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>53729</t>
+          <t>55278</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>58938</t>
+          <t>59731</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>95094</t>
+          <t>96221</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>98061</t>
+          <t>97932</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>141271</t>
+          <t>142134</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>527256</t>
+          <t>527169</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>553524</t>
+          <t>553188</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>639923</t>
+          <t>637539</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>682299</t>
+          <t>679914</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1177889</t>
+          <t>1176397</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1228298</t>
+          <t>1226101</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -10816,7 +10816,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se le escapa la orina (incontinencia) en 2023</t>
+          <t>Población según si se le escapa la orina (incontinencia) en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11026,82 +11026,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3504</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6293</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3384</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2753</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6383</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -11124,12 +11124,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3749</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>11884</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11139,12 +11139,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11159,12 +11159,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>9880</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11174,12 +11174,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11194,12 +11194,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18999</t>
+          <t>20532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11209,12 +11209,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93099</t>
+          <t>93367</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>102213</t>
+          <t>102124</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54759</t>
+          <t>54397</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61531</t>
+          <t>61744</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>150619</t>
+          <t>150231</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>162392</t>
+          <t>162431</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11537,12 +11537,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -11580,12 +11580,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11595,12 +11595,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11615,12 +11615,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2159</t>
+          <t>2205</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>7851</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11630,12 +11630,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5446</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>15147</t>
+          <t>14676</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84203</t>
+          <t>84696</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92237</t>
+          <t>92341</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38019</t>
+          <t>37724</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44313</t>
+          <t>44046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124909</t>
+          <t>125039</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134984</t>
+          <t>135058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -11923,12 +11923,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>601</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11958,12 +11958,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>5828</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11973,12 +11973,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -12036,12 +12036,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18781</t>
+          <t>19048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12051,12 +12051,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8538</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>11671</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24105</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80628</t>
+          <t>80838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>91819</t>
+          <t>92175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41235</t>
+          <t>41060</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48507</t>
+          <t>48591</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124201</t>
+          <t>125346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138210</t>
+          <t>138570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3250</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -12394,7 +12394,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -12414,12 +12414,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>382</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12095</t>
+          <t>12054</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12429,12 +12429,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12449,12 +12449,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2773</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18628</t>
+          <t>18107</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12464,12 +12464,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -12492,12 +12492,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12163</t>
+          <t>12503</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25570</t>
+          <t>25786</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12507,12 +12507,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12527,12 +12527,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34674</t>
+          <t>34208</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12542,12 +12542,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12562,12 +12562,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10463</t>
+          <t>9423</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51349</t>
+          <t>49788</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>204208</t>
+          <t>204808</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>219111</t>
+          <t>219426</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>280884</t>
+          <t>281425</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>323124</t>
+          <t>322826</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>495661</t>
+          <t>498247</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>550327</t>
+          <t>551065</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -12835,12 +12835,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12870,12 +12870,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13239</t>
+          <t>13552</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12885,12 +12885,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12905,12 +12905,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8361</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>18422</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12920,12 +12920,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -12948,12 +12948,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13455</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12983,12 +12983,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22950</t>
+          <t>22983</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36588</t>
+          <t>37131</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12998,12 +12998,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13018,12 +13018,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>30039</t>
+          <t>29741</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46253</t>
+          <t>46274</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13033,7 +13033,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75090</t>
+          <t>75324</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84659</t>
+          <t>84924</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>159356</t>
+          <t>158866</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>174606</t>
+          <t>174202</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>237411</t>
+          <t>237202</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>255573</t>
+          <t>255991</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,15%</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13326,12 +13326,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16601</t>
+          <t>16395</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>30122</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13341,47 +13341,47 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>23446</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>16773</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>31094</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>5,17%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>23446</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>17268</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>30881</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,59%</t>
         </is>
       </c>
     </row>
@@ -13404,12 +13404,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13419,12 +13419,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13439,12 +13439,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30609</t>
+          <t>30636</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48086</t>
+          <t>47557</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31512</t>
+          <t>30839</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48910</t>
+          <t>48210</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13489,12 +13489,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -13517,7 +13517,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>911</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>249019</t>
+          <t>249963</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>269644</t>
+          <t>269649</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13567,7 +13567,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13587,12 +13587,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>250956</t>
+          <t>250378</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>271675</t>
+          <t>272495</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13602,12 +13602,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,03%</t>
         </is>
       </c>
     </row>
@@ -13747,12 +13747,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11762</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24931</t>
+          <t>23188</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13762,12 +13762,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13782,12 +13782,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19857</t>
+          <t>18129</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>53250</t>
+          <t>52851</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13797,12 +13797,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13817,12 +13817,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36359</t>
+          <t>36500</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>69537</t>
+          <t>69242</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -13860,12 +13860,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>39731</t>
+          <t>40938</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>61198</t>
+          <t>61926</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13875,12 +13875,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13895,12 +13895,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>51536</t>
+          <t>46426</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>126039</t>
+          <t>124204</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13910,12 +13910,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>99143</t>
+          <t>93755</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>172490</t>
+          <t>171299</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13945,12 +13945,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -13973,12 +13973,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>557469</t>
+          <t>557564</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>582415</t>
+          <t>580397</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13988,12 +13988,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14008,12 +14008,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>841731</t>
+          <t>844011</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>944950</t>
+          <t>948795</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14023,12 +14023,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14043,12 +14043,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1418184</t>
+          <t>1419404</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1515270</t>
+          <t>1527559</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14058,12 +14058,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5409-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5409-Clase-trans_orig.xlsx
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53544</t>
+          <t>54404</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>83166</t>
+          <t>82978</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>920</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8997</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1599</t>
+          <t>1644</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11165</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>60648</t>
+          <t>61383</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69884</t>
+          <t>69400</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15754</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>23238</t>
+          <t>23242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80357</t>
+          <t>80225</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91482</t>
+          <t>91624</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,41%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>836</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>7287</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>10967</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9891</t>
+          <t>10955</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25231</t>
+          <t>25709</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>14199</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32093</t>
+          <t>31027</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>231508</t>
+          <t>230719</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>247575</t>
+          <t>247005</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>72734</t>
+          <t>73266</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83434</t>
+          <t>83483</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>307217</t>
+          <t>308715</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>327389</t>
+          <t>327757</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,78%</t>
         </is>
       </c>
     </row>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9822</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>1734</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>11743</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1739</t>
+          <t>1826</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>9788</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4446</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17265</t>
+          <t>17186</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7725</t>
+          <t>7436</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22109</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42513</t>
+          <t>43221</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52683</t>
+          <t>52709</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>74444</t>
+          <t>75737</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89181</t>
+          <t>89822</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>122758</t>
+          <t>123035</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>140201</t>
+          <t>140335</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6801</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22244</t>
+          <t>23419</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6693</t>
+          <t>7468</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23024</t>
+          <t>22711</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>16351</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37810</t>
+          <t>35927</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,47 +3176,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>25479</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>16502</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>38112</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
           <t>8,89%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>25479</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>17252</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>37473</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>372180</t>
+          <t>373177</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>397788</t>
+          <t>397412</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>376382</t>
+          <t>375688</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>401565</t>
+          <t>400669</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2557</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12363</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31630</t>
+          <t>33402</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>17666</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>40066</t>
+          <t>39525</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19899</t>
+          <t>19370</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>40277</t>
+          <t>38831</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29389</t>
+          <t>28881</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>54812</t>
+          <t>54270</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>53425</t>
+          <t>52596</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>84061</t>
+          <t>84095</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>455979</t>
+          <t>456828</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>477175</t>
+          <t>477518</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>599640</t>
+          <t>597355</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>629432</t>
+          <t>629313</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1063805</t>
+          <t>1062931</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1100381</t>
+          <t>1099887</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9852</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4292,7 +4292,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>7246</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1055</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>12270</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34724</t>
+          <t>34066</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18364</t>
+          <t>18043</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>57300</t>
+          <t>56937</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>68152</t>
+          <t>68144</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10049</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>5299</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11732</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4813,12 +4813,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50581</t>
+          <t>50623</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59554</t>
+          <t>59564</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>12471</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66229</t>
+          <t>66455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77333</t>
+          <t>77366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6902</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -5184,12 +5184,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>15191</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5199,12 +5199,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9386</t>
+          <t>9436</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5234,12 +5234,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5044</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18730</t>
+          <t>19736</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5269,12 +5269,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,39%</t>
         </is>
       </c>
     </row>
@@ -5297,12 +5297,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102635</t>
+          <t>102763</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115667</t>
+          <t>115765</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43436</t>
+          <t>43399</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>52645</t>
+          <t>52660</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5347,12 +5347,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>152076</t>
+          <t>151228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>167114</t>
+          <t>166243</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -5527,12 +5527,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2119</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13647</t>
+          <t>11720</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -5640,12 +5640,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15120</t>
+          <t>14563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37386</t>
+          <t>37614</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15515</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5710,12 +5710,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21890</t>
+          <t>21766</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45882</t>
+          <t>44548</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>187949</t>
+          <t>188626</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>212238</t>
+          <t>212208</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41857</t>
+          <t>41889</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54570</t>
+          <t>54938</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>238045</t>
+          <t>238398</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>262803</t>
+          <t>262668</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,0%</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5988,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12046</t>
+          <t>11943</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29505</t>
+          <t>29169</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13846</t>
+          <t>13583</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32401</t>
+          <t>32326</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>4254</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>15595</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>12290</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29070</t>
+          <t>30120</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20152</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38967</t>
+          <t>42026</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -6209,12 +6209,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>84351</t>
+          <t>83481</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97346</t>
+          <t>97426</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>136227</t>
+          <t>135512</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>159354</t>
+          <t>158298</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>226427</t>
+          <t>226271</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>252660</t>
+          <t>253019</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13831</t>
+          <t>13797</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>33211</t>
+          <t>33832</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13904</t>
+          <t>14193</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33125</t>
+          <t>34872</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26771</t>
+          <t>27231</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51826</t>
+          <t>50747</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27122</t>
+          <t>26631</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50431</t>
+          <t>50146</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -6700,12 +6700,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>318526</t>
+          <t>317753</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>348160</t>
+          <t>347739</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6715,47 +6715,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>88,1%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>336436</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>320522</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>349908</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>84,81%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>80,8%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>88,21%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>336436</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>321152</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>350663</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>84,81%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>80,96%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>88,4%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>17561</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>34843</t>
+          <t>33569</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62451</t>
+          <t>62625</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>42560</t>
+          <t>42940</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>73279</t>
+          <t>74157</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29896</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>59091</t>
+          <t>61720</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7043,12 +7043,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>57175</t>
+          <t>59354</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>90047</t>
+          <t>92358</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>98558</t>
+          <t>97316</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>142096</t>
+          <t>142653</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -7121,12 +7121,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>490906</t>
+          <t>488107</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>521194</t>
+          <t>518090</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>602435</t>
+          <t>599859</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>641473</t>
+          <t>641024</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1097573</t>
+          <t>1099964</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1149817</t>
+          <t>1151838</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7206,12 +7206,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,49%</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12771</t>
+          <t>12609</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10637</t>
+          <t>10806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7748,12 +7748,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17811</t>
+          <t>18270</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55876</t>
+          <t>56038</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67155</t>
+          <t>67133</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>26251</t>
+          <t>26082</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35611</t>
+          <t>35539</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7861,12 +7861,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>87724</t>
+          <t>87265</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>100989</t>
+          <t>101387</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7896,12 +7896,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>10217</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -8154,12 +8154,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>874</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7422</t>
+          <t>7035</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4814</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>9157</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -8267,12 +8267,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45922</t>
+          <t>46309</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52483</t>
+          <t>52470</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8282,12 +8282,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>8826</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8317,7 +8317,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8337,12 +8337,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57473</t>
+          <t>57786</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68922</t>
+          <t>68929</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8352,12 +8352,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -8610,12 +8610,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11672</t>
+          <t>12622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8625,12 +8625,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8645,12 +8645,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>1233</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8660,12 +8660,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8680,12 +8680,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5889</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106286</t>
+          <t>105867</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116797</t>
+          <t>116144</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35524</t>
+          <t>35419</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45109</t>
+          <t>44976</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8773,12 +8773,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146259</t>
+          <t>146341</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>159439</t>
+          <t>159647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8808,12 +8808,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,9%</t>
         </is>
       </c>
     </row>
@@ -8953,12 +8953,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>842</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8833</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13133</t>
+          <t>13007</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9023,12 +9023,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4704</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17621</t>
+          <t>17695</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9038,12 +9038,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20885</t>
+          <t>22571</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9081,12 +9081,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9101,12 +9101,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3669</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18426</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9136,12 +9136,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13802</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32229</t>
+          <t>33220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9151,12 +9151,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -9179,12 +9179,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178562</t>
+          <t>176950</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>193255</t>
+          <t>192947</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9194,12 +9194,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>74143</t>
+          <t>73949</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90905</t>
+          <t>90953</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>258689</t>
+          <t>259416</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>281069</t>
+          <t>281376</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9264,12 +9264,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -9409,12 +9409,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9444,12 +9444,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13399</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9479,12 +9479,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19544</t>
+          <t>18364</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9494,12 +9494,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>7240</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21013</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9557,12 +9557,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25284</t>
+          <t>25146</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9592,12 +9592,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20088</t>
+          <t>19439</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>41382</t>
+          <t>40782</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -9635,12 +9635,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>120583</t>
+          <t>120328</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134663</t>
+          <t>134853</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9650,12 +9650,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>126724</t>
+          <t>126651</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>146429</t>
+          <t>145734</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>250646</t>
+          <t>254040</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>276186</t>
+          <t>277445</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>91,03%</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11782</t>
+          <t>11773</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31497</t>
+          <t>32031</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9935,12 +9935,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11782</t>
+          <t>11773</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31497</t>
+          <t>32031</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29558</t>
+          <t>30374</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57023</t>
+          <t>57018</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10028,7 +10028,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>29558</t>
+          <t>30374</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57023</t>
+          <t>57018</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10063,7 +10063,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>333382</t>
+          <t>333338</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>365662</t>
+          <t>366309</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>333382</t>
+          <t>333338</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>365662</t>
+          <t>366309</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -10321,12 +10321,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>4372</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>15601</t>
+          <t>15683</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10336,12 +10336,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23755</t>
+          <t>23288</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>49539</t>
+          <t>49798</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>30484</t>
+          <t>30677</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>58560</t>
+          <t>58469</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10434,12 +10434,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>30442</t>
+          <t>30306</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>55278</t>
+          <t>53955</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10449,12 +10449,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10469,12 +10469,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>59731</t>
+          <t>59762</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>96221</t>
+          <t>95008</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>97932</t>
+          <t>98420</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>142134</t>
+          <t>142274</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -10547,12 +10547,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>527169</t>
+          <t>527034</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>553188</t>
+          <t>553530</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10582,12 +10582,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>637539</t>
+          <t>637991</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>679914</t>
+          <t>681299</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10597,12 +10597,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10617,12 +10617,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1176397</t>
+          <t>1177196</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1226101</t>
+          <t>1226333</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10632,12 +10632,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,32%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,93%</t>
         </is>
       </c>
     </row>
@@ -11006,32 +11006,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2102</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>748</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11076,32 +11076,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2838</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>984</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -11119,32 +11119,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>8155</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11884</t>
+          <t>14157</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11154,32 +11154,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>7119</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9880</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11189,32 +11189,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>13146</t>
+          <t>15274</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20532</t>
+          <t>22315</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -11232,32 +11232,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>98354</t>
+          <t>110156</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>93367</t>
+          <t>103952</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>102124</t>
+          <t>114528</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11267,32 +11267,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58647</t>
+          <t>66692</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>54397</t>
+          <t>61647</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61744</t>
+          <t>70261</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11302,32 +11302,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>157001</t>
+          <t>176847</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>150231</t>
+          <t>169253</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>162431</t>
+          <t>182413</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,56%</t>
         </is>
       </c>
     </row>
@@ -11345,17 +11345,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11380,17 +11380,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11415,17 +11415,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -11507,12 +11507,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3562</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -11522,7 +11522,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11532,32 +11532,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>586</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -11575,22 +11575,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8856</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -11600,7 +11600,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11610,32 +11610,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2205</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11645,32 +11645,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>9119</t>
+          <t>10810</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14676</t>
+          <t>17030</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -11688,32 +11688,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>89291</t>
+          <t>98571</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84696</t>
+          <t>93463</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92341</t>
+          <t>101666</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>41450</t>
+          <t>48602</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37724</t>
+          <t>44538</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44046</t>
+          <t>51780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>130741</t>
+          <t>147173</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125039</t>
+          <t>140857</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>135058</t>
+          <t>151965</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -11801,17 +11801,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11836,17 +11836,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11871,17 +11871,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11918,32 +11918,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>577</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5730</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11953,32 +11953,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5828</t>
+          <t>6445</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11988,27 +11988,27 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5466</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2635</t>
+          <t>2711</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9496</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -12031,32 +12031,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12864</t>
+          <t>13657</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19048</t>
+          <t>19878</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>10387</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17391</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>13382</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24273</t>
+          <t>27318</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,03%</t>
         </is>
       </c>
     </row>
@@ -12144,32 +12144,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>86826</t>
+          <t>96309</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80838</t>
+          <t>89588</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92175</t>
+          <t>102015</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12179,32 +12179,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>45510</t>
+          <t>49619</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41060</t>
+          <t>44822</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>48591</t>
+          <t>53248</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>132336</t>
+          <t>145928</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>125346</t>
+          <t>136613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>138570</t>
+          <t>152438</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -12257,17 +12257,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12292,17 +12292,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12374,32 +12374,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3845</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12409,32 +12409,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3567</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12444,32 +12444,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>11319</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18107</t>
+          <t>16426</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -12487,32 +12487,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>19597</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>12620</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25786</t>
+          <t>27869</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12522,32 +12522,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>8148</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34208</t>
+          <t>17730</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12557,32 +12557,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>29633</t>
+          <t>31800</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>23831</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49788</t>
+          <t>41072</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -12600,32 +12600,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>212922</t>
+          <t>232615</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>204808</t>
+          <t>222815</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>219426</t>
+          <t>240183</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12635,32 +12635,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>311061</t>
+          <t>113884</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>281425</t>
+          <t>107670</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>322826</t>
+          <t>118526</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12670,32 +12670,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>523983</t>
+          <t>346499</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>498247</t>
+          <t>336624</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>551065</t>
+          <t>356513</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>91,5%</t>
         </is>
       </c>
     </row>
@@ -12713,17 +12713,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>237592</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>237592</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>237592</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12748,17 +12748,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>326143</t>
+          <t>130265</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>326143</t>
+          <t>130265</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>326143</t>
+          <t>130265</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12783,17 +12783,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>563735</t>
+          <t>389618</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>563735</t>
+          <t>389618</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>563735</t>
+          <t>389618</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12830,32 +12830,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7568</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12865,67 +12865,67 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13552</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>13119</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>8602</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>19036</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
           <t>2,68%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>6,61%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>12366</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>8299</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>18422</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -12943,32 +12943,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7650</t>
+          <t>8370</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>14264</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12978,32 +12978,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29327</t>
+          <t>31409</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22983</t>
+          <t>24160</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37131</t>
+          <t>39238</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13013,32 +13013,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>36977</t>
+          <t>39780</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>29741</t>
+          <t>31246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46274</t>
+          <t>48926</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -13056,32 +13056,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>80702</t>
+          <t>88718</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>75324</t>
+          <t>82802</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84924</t>
+          <t>93630</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13091,17 +13091,17 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>167094</t>
+          <t>179420</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>158866</t>
+          <t>171191</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>174202</t>
+          <t>187559</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,45%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13126,32 +13126,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>247796</t>
+          <t>268138</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>237202</t>
+          <t>257127</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>255991</t>
+          <t>277449</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,42%</t>
         </is>
       </c>
     </row>
@@ -13169,17 +13169,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13204,17 +13204,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>205133</t>
+          <t>220244</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13239,17 +13239,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>297139</t>
+          <t>321037</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -13296,12 +13296,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2275</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -13311,7 +13311,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13321,32 +13321,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22354</t>
+          <t>25690</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>18887</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30122</t>
+          <t>35493</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13356,32 +13356,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>23446</t>
+          <t>26871</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16773</t>
+          <t>19848</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>31094</t>
+          <t>35485</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -13434,32 +13434,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>38876</t>
+          <t>42228</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30636</t>
+          <t>33469</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47557</t>
+          <t>51650</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13469,32 +13469,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>38876</t>
+          <t>42228</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30839</t>
+          <t>34144</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>48210</t>
+          <t>53073</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -13512,27 +13512,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13547,32 +13547,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>259849</t>
+          <t>277257</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>249963</t>
+          <t>265215</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>269649</t>
+          <t>288186</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13582,32 +13582,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>261961</t>
+          <t>279352</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>250378</t>
+          <t>267616</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>272495</t>
+          <t>291110</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,54%</t>
         </is>
       </c>
     </row>
@@ -13625,17 +13625,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13660,17 +13660,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>321079</t>
+          <t>345175</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>321079</t>
+          <t>345175</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>321079</t>
+          <t>345175</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13695,17 +13695,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>324283</t>
+          <t>348451</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>324283</t>
+          <t>348451</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>324283</t>
+          <t>348451</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13742,32 +13742,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>16865</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>11666</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23188</t>
+          <t>25180</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13777,32 +13777,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>39019</t>
+          <t>44035</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18129</t>
+          <t>35009</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>52851</t>
+          <t>55058</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13812,32 +13812,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>55884</t>
+          <t>61729</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36500</t>
+          <t>51355</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>69242</t>
+          <t>77451</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -13855,32 +13855,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>50376</t>
+          <t>54850</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>40938</t>
+          <t>43554</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>61926</t>
+          <t>67725</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13890,32 +13890,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>94767</t>
+          <t>104089</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>46426</t>
+          <t>91224</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>124204</t>
+          <t>119796</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13925,32 +13925,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>145142</t>
+          <t>158940</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>93755</t>
+          <t>140760</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>171299</t>
+          <t>179672</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>11,34%</t>
         </is>
       </c>
     </row>
@@ -13968,32 +13968,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>570207</t>
+          <t>628466</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>557564</t>
+          <t>614766</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>580397</t>
+          <t>641547</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14003,32 +14003,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>883611</t>
+          <t>735473</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>844011</t>
+          <t>717670</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>948795</t>
+          <t>751917</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14038,32 +14038,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1453817</t>
+          <t>1363939</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1419404</t>
+          <t>1340886</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1527559</t>
+          <t>1384502</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>87,37%</t>
         </is>
       </c>
     </row>
@@ -14081,17 +14081,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>637448</t>
+          <t>701010</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>637448</t>
+          <t>701010</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>637448</t>
+          <t>701010</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14116,17 +14116,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>1017396</t>
+          <t>883598</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1017396</t>
+          <t>883598</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>1017396</t>
+          <t>883598</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14151,17 +14151,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1654843</t>
+          <t>1584608</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1654843</t>
+          <t>1584608</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1654843</t>
+          <t>1584608</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
